--- a/Game/Person.xlsx
+++ b/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252 Patch 2</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
